--- a/dev_docs/Tetra数值公式_11_4.xlsx
+++ b/dev_docs/Tetra数值公式_11_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCL\.minecraft\versions\SenDims_BanForges\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA9DF8D-237C-4923-BCF9-D1B71C5DA3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9DC169-E8C4-4BC9-96AF-3956235E5830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="1500" windowWidth="15620" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="291">
   <si>
     <t>刀刃</t>
   </si>
@@ -651,9 +651,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>'quark:myalite_crystal'</t>
-  </si>
-  <si>
     <t>幻境石水晶</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -662,9 +659,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>'enderio:end_steel_ingot'</t>
-  </si>
-  <si>
     <t>2.3.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -691,9 +685,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>'integrateddynamics:crystalized_chorus_chunk'</t>
-  </si>
-  <si>
     <t>2.1.2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -773,6 +764,225 @@
   </si>
   <si>
     <t>#forge:ingots/desh'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎狱尖塔块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'ad_astra:infernal_spire_block'</t>
+  </si>
+  <si>
+    <t>耐热金属</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.1.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kubejs:virtual_gold_ingot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>御腐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵豪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗忆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>极限合金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铍青铜合金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三项合金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kubejs:trinity_alloy_ingot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kubejs:beryllium_bronze_alloy_ingot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/neutronium'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/forgotten_metal'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/regalium'</t>
+  </si>
+  <si>
+    <t>'#forge:ingots/utherium'</t>
+  </si>
+  <si>
+    <t>'enderio:end_steel_ingot'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/calorite'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'#forge:ingots/extreme'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'quark:myalite_crystal'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆裂紫颂果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>integrateddynamics:crystalized_chorus_chunk'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minecraft:popped_chorus_fruit'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+1.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性+0.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲穿透+2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抵抗+0.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值+4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盔甲撕裂+5%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验获取+0.15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害+0.05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害+3%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度-5%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲穿透+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值+3%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盔甲撕裂+3%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招架治疗量+333</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.035</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜伤害+3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊行动冷却+0.05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动力效率+8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜伤害+6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -950,7 +1160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1040,6 +1250,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1317,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T138"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.58203125" style="2" customWidth="1"/>
@@ -1705,7 +1918,7 @@
         <v>3.25</v>
       </c>
       <c r="K11" s="10">
-        <f t="shared" ref="K11:K93" si="2">(G11*$I$5)+(H11*$I$6)+(I11*$I$7)</f>
+        <f t="shared" ref="K11:K101" si="2">(G11*$I$5)+(H11*$I$6)+(I11*$I$7)</f>
         <v>1.3</v>
       </c>
       <c r="L11" s="12">
@@ -1815,11 +2028,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="M13" s="13">
-        <f t="shared" ref="M13:M94" si="10">I13*$M$2</f>
+        <f t="shared" ref="M13:M102" si="10">I13*$M$2</f>
         <v>6.8750000000000009</v>
       </c>
       <c r="N13" s="13">
-        <f t="shared" ref="N13:N94" si="11">I13*$M$3</f>
+        <f t="shared" ref="N13:N102" si="11">I13*$M$3</f>
         <v>1.6500000000000001</v>
       </c>
       <c r="O13" s="10">
@@ -2195,7 +2408,7 @@
         <v>0.9</v>
       </c>
       <c r="J20" s="23">
-        <f t="shared" ref="J20:J102" si="12">(G20*$I$2)+(H20*$I$3)</f>
+        <f t="shared" ref="J20:J110" si="12">(G20*$I$2)+(H20*$I$3)</f>
         <v>2.75</v>
       </c>
       <c r="K20" s="10">
@@ -3581,13 +3794,13 @@
     <row r="46" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="4"/>
       <c r="D46" s="32" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G46" s="16">
         <v>2</v>
@@ -3625,7 +3838,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="R46" s="10"/>
       <c r="S46" s="10"/>
@@ -4266,23 +4479,23 @@
         <v>3.2</v>
       </c>
       <c r="J58" s="23">
-        <f t="shared" ref="J58:J81" si="28">(G58*$I$2)+(H58*$I$3)</f>
+        <f t="shared" ref="J58:J89" si="28">(G58*$I$2)+(H58*$I$3)</f>
         <v>15.6</v>
       </c>
       <c r="K58" s="10">
-        <f t="shared" ref="K58:K81" si="29">(G58*$I$5)+(H58*$I$6)+(I58*$I$7)</f>
+        <f t="shared" ref="K58:K89" si="29">(G58*$I$5)+(H58*$I$6)+(I58*$I$7)</f>
         <v>6.15</v>
       </c>
       <c r="L58" s="12">
-        <f t="shared" ref="L58:L81" si="30">J58+K58</f>
+        <f t="shared" ref="L58:L89" si="30">J58+K58</f>
         <v>21.75</v>
       </c>
       <c r="M58" s="13">
-        <f t="shared" ref="M58:M81" si="31">I58*$M$2</f>
+        <f t="shared" ref="M58:M89" si="31">I58*$M$2</f>
         <v>20</v>
       </c>
       <c r="N58" s="13">
-        <f t="shared" ref="N58:N81" si="32">I58*$M$3</f>
+        <f t="shared" ref="N58:N89" si="32">I58*$M$3</f>
         <v>4.8000000000000007</v>
       </c>
       <c r="O58" s="10">
@@ -4310,13 +4523,13 @@
         <v>187</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G59" s="4">
         <v>5.5</v>
@@ -4354,23 +4567,23 @@
         <v>2</v>
       </c>
       <c r="Q59" s="26" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
     </row>
     <row r="60" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="D60" s="29" t="s">
-        <v>222</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G60" s="4">
         <v>3</v>
@@ -4408,10 +4621,10 @@
         <v>1</v>
       </c>
       <c r="Q60" s="26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="R60" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="S60" s="10"/>
     </row>
@@ -4423,16 +4636,16 @@
         <v>20</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G61" s="4">
         <v>7.5</v>
@@ -4470,7 +4683,7 @@
         <v>2</v>
       </c>
       <c r="Q61" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
@@ -4486,13 +4699,13 @@
         <v>188</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G62" s="9">
         <v>7</v>
@@ -4530,659 +4743,1129 @@
         <v>3</v>
       </c>
       <c r="Q62" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="R62" s="10"/>
       <c r="S62" s="10"/>
     </row>
     <row r="63" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="26" t="s">
+      <c r="A63" s="2">
+        <v>29</v>
+      </c>
+      <c r="B63" s="2">
+        <v>30</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
+      <c r="D63" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" s="4">
+        <v>9</v>
+      </c>
+      <c r="H63" s="4">
+        <v>6</v>
+      </c>
+      <c r="I63" s="4">
+        <v>4</v>
+      </c>
       <c r="J63" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K63" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="L63" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="M63" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N63" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="O63" s="10">
+        <v>4</v>
+      </c>
+      <c r="P63" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q63" s="26" t="s">
+        <v>266</v>
+      </c>
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
     </row>
     <row r="64" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="10"/>
-      <c r="D64" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E64" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="H64" s="4">
+        <v>7</v>
+      </c>
+      <c r="I64" s="4">
+        <v>4.8</v>
+      </c>
       <c r="J64" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" ref="J64:J70" si="33">(G64*$I$2)+(H64*$I$3)</f>
+        <v>22.7</v>
       </c>
       <c r="K64" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" ref="K64:K70" si="34">(G64*$I$5)+(H64*$I$6)+(I64*$I$7)</f>
+        <v>8.3000000000000007</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="L64:L70" si="35">J64+K64</f>
+        <v>31</v>
       </c>
       <c r="M64" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="M64:M70" si="36">I64*$M$2</f>
+        <v>30</v>
       </c>
       <c r="N64" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
+        <f t="shared" ref="N64:N70" si="37">I64*$M$3</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="O64" s="10">
+        <v>5</v>
+      </c>
+      <c r="P64" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q64" s="26" t="s">
+        <v>267</v>
+      </c>
       <c r="R64" s="10"/>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E65" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="23"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="13"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-      <c r="Q65" s="10"/>
+    <row r="65" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="4"/>
+      <c r="D65" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="4">
+        <v>8</v>
+      </c>
+      <c r="H65" s="4">
+        <v>12</v>
+      </c>
+      <c r="I65" s="4">
+        <v>4</v>
+      </c>
+      <c r="J65" s="23">
+        <f t="shared" si="33"/>
+        <v>22</v>
+      </c>
+      <c r="K65" s="10">
+        <f t="shared" si="34"/>
+        <v>10</v>
+      </c>
+      <c r="L65" s="12">
+        <f t="shared" si="35"/>
+        <v>32</v>
+      </c>
+      <c r="M65" s="13">
+        <f t="shared" si="36"/>
+        <v>25</v>
+      </c>
+      <c r="N65" s="13">
+        <f t="shared" si="37"/>
+        <v>6</v>
+      </c>
+      <c r="O65" s="10">
+        <v>5</v>
+      </c>
+      <c r="P65" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q65" s="26" t="s">
+        <v>269</v>
+      </c>
       <c r="R65" s="10"/>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="26"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="23"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
+    <row r="66" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>35</v>
+      </c>
+      <c r="B66" s="2">
+        <v>40</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="F66" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="30">
+        <v>9</v>
+      </c>
+      <c r="H66" s="30">
+        <v>12</v>
+      </c>
+      <c r="I66" s="30">
+        <v>6</v>
+      </c>
+      <c r="J66" s="23">
+        <f t="shared" si="33"/>
+        <v>24</v>
+      </c>
+      <c r="K66" s="10">
+        <f t="shared" si="34"/>
+        <v>10.5</v>
+      </c>
+      <c r="L66" s="12">
+        <f t="shared" si="35"/>
+        <v>34.5</v>
+      </c>
+      <c r="M66" s="13">
+        <f t="shared" si="36"/>
+        <v>37.5</v>
+      </c>
+      <c r="N66" s="13">
+        <f t="shared" si="37"/>
+        <v>9</v>
+      </c>
+      <c r="O66" s="10">
+        <v>4</v>
+      </c>
+      <c r="P66" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="26" t="s">
+        <v>270</v>
+      </c>
       <c r="R66" s="10"/>
       <c r="S66" s="10"/>
     </row>
-    <row r="67" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="E67" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="23"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-    </row>
-    <row r="68" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="26"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="12"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="10"/>
+    <row r="67" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="30"/>
+      <c r="D67" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F67" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G67" s="30">
+        <v>12</v>
+      </c>
+      <c r="H67" s="30">
+        <v>5</v>
+      </c>
+      <c r="I67" s="30">
+        <v>6.5</v>
+      </c>
+      <c r="J67" s="23">
+        <f t="shared" si="33"/>
+        <v>26.5</v>
+      </c>
+      <c r="K67" s="10">
+        <f t="shared" si="34"/>
+        <v>8.5</v>
+      </c>
+      <c r="L67" s="12">
+        <f t="shared" si="35"/>
+        <v>35</v>
+      </c>
+      <c r="M67" s="13">
+        <f t="shared" si="36"/>
+        <v>40.625</v>
+      </c>
+      <c r="N67" s="13">
+        <f t="shared" si="37"/>
+        <v>9.75</v>
+      </c>
+      <c r="O67" s="10">
+        <v>4</v>
+      </c>
+      <c r="P67" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q67" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="R67" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="S67" s="26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>40</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" s="4">
+        <v>14</v>
+      </c>
+      <c r="H68" s="4">
+        <v>6</v>
+      </c>
+      <c r="I68" s="4">
+        <v>7</v>
+      </c>
+      <c r="J68" s="23">
+        <f t="shared" si="33"/>
+        <v>31</v>
+      </c>
+      <c r="K68" s="10">
+        <f t="shared" si="34"/>
+        <v>10</v>
+      </c>
+      <c r="L68" s="12">
+        <f t="shared" si="35"/>
+        <v>41</v>
+      </c>
+      <c r="M68" s="13">
+        <f t="shared" si="36"/>
+        <v>43.75</v>
+      </c>
+      <c r="N68" s="13">
+        <f t="shared" si="37"/>
+        <v>10.5</v>
+      </c>
+      <c r="O68" s="10">
+        <v>6</v>
+      </c>
+      <c r="P68" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="R68" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
+    <row r="69" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
       <c r="J69" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K69" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M69" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N69" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="10">
+        <v>6</v>
+      </c>
+      <c r="P69" s="10">
+        <v>6</v>
+      </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
       <c r="S69" s="10"/>
     </row>
-    <row r="70" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
+    <row r="70" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>45</v>
+      </c>
+      <c r="B70" s="2">
+        <v>50</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" s="30">
+        <v>15.5</v>
+      </c>
+      <c r="H70" s="30">
+        <v>6</v>
+      </c>
+      <c r="I70" s="30">
+        <v>8</v>
+      </c>
       <c r="J70" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="33"/>
+        <v>34</v>
       </c>
       <c r="K70" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>10.75</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>44.75</v>
       </c>
       <c r="M70" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>50</v>
       </c>
       <c r="N70" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
-      <c r="R70" s="10"/>
+        <f t="shared" si="37"/>
+        <v>12</v>
+      </c>
+      <c r="O70" s="10">
+        <v>6</v>
+      </c>
+      <c r="P70" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="R70" s="26" t="s">
+        <v>227</v>
+      </c>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E71" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
+    <row r="71" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>40</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="4">
+        <v>14</v>
+      </c>
+      <c r="H71" s="4">
+        <v>5</v>
+      </c>
+      <c r="I71" s="4">
+        <v>7.5</v>
+      </c>
       <c r="J71" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="K71" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="L71" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M71" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>46.875</v>
       </c>
       <c r="N71" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O71" s="10"/>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="10"/>
+        <v>11.25</v>
+      </c>
+      <c r="O71" s="10">
+        <v>6</v>
+      </c>
+      <c r="P71" s="10">
+        <v>7</v>
+      </c>
+      <c r="Q71" s="26" t="s">
+        <v>274</v>
+      </c>
       <c r="R71" s="10"/>
       <c r="S71" s="10"/>
     </row>
-    <row r="72" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
+    <row r="72" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>50</v>
+      </c>
+      <c r="B72" s="2">
+        <v>60</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="F72" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" s="30">
+        <v>17</v>
+      </c>
+      <c r="H72" s="30">
+        <v>7</v>
+      </c>
+      <c r="I72" s="30">
+        <v>9.5</v>
+      </c>
       <c r="J72" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L72" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="M72" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>59.375</v>
       </c>
       <c r="N72" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
+        <v>14.25</v>
+      </c>
+      <c r="O72" s="10">
+        <v>7</v>
+      </c>
+      <c r="P72" s="10">
+        <v>7</v>
+      </c>
+      <c r="Q72" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="R72" s="10"/>
       <c r="S72" s="10"/>
     </row>
-    <row r="73" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E73" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
+    <row r="73" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="30"/>
+      <c r="D73" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F73" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="30">
+        <v>18</v>
+      </c>
+      <c r="H73" s="30">
+        <v>10</v>
+      </c>
+      <c r="I73" s="30">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="J73" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" ref="J73:J78" si="38">(G73*$I$2)+(H73*$I$3)</f>
+        <v>41</v>
       </c>
       <c r="K73" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" ref="K73:K78" si="39">(G73*$I$5)+(H73*$I$6)+(I73*$I$7)</f>
+        <v>14</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="L73:L78" si="40">J73+K73</f>
+        <v>55</v>
       </c>
       <c r="M73" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="M73:M78" si="41">I73*$M$2</f>
+        <v>61.250000000000007</v>
       </c>
       <c r="N73" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
+        <f t="shared" ref="N73:N78" si="42">I73*$M$3</f>
+        <v>14.700000000000001</v>
+      </c>
+      <c r="O73" s="10">
+        <v>7</v>
+      </c>
+      <c r="P73" s="10">
+        <v>7</v>
+      </c>
+      <c r="Q73" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="R73" s="26" t="s">
+        <v>231</v>
+      </c>
       <c r="S73" s="10"/>
     </row>
-    <row r="74" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="26"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
+    <row r="74" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>60</v>
+      </c>
+      <c r="B74" s="2">
+        <v>65</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="4">
+        <v>20</v>
+      </c>
+      <c r="H74" s="4">
+        <v>10</v>
+      </c>
+      <c r="I74" s="4">
+        <v>10</v>
+      </c>
       <c r="J74" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>45</v>
       </c>
       <c r="K74" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>15</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>60</v>
       </c>
       <c r="M74" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>62.5</v>
       </c>
       <c r="N74" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
-      <c r="R74" s="10"/>
+        <f t="shared" si="42"/>
+        <v>15</v>
+      </c>
+      <c r="O74" s="10">
+        <v>8</v>
+      </c>
+      <c r="P74" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="R74" s="26" t="s">
+        <v>277</v>
+      </c>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
+    <row r="75" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="4"/>
+      <c r="D75" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G75" s="4">
+        <v>23</v>
+      </c>
+      <c r="H75" s="4">
+        <v>8</v>
+      </c>
+      <c r="I75" s="4">
+        <v>11</v>
+      </c>
       <c r="J75" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>50</v>
       </c>
       <c r="K75" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>15.5</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>65.5</v>
       </c>
       <c r="M75" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>68.75</v>
       </c>
       <c r="N75" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O75" s="10"/>
-      <c r="P75" s="10"/>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
+        <f t="shared" si="42"/>
+        <v>16.5</v>
+      </c>
+      <c r="O75" s="10">
+        <v>8</v>
+      </c>
+      <c r="P75" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q75" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="R75" s="26" t="s">
+        <v>280</v>
+      </c>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
+    <row r="76" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="4"/>
+      <c r="D76" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="4">
+        <v>17</v>
+      </c>
+      <c r="H76" s="4">
+        <v>18</v>
+      </c>
+      <c r="I76" s="4">
+        <v>10</v>
+      </c>
       <c r="J76" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>43</v>
       </c>
       <c r="K76" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>17.5</v>
       </c>
       <c r="L76" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>60.5</v>
       </c>
       <c r="M76" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>62.5</v>
       </c>
       <c r="N76" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
-      <c r="R76" s="10"/>
+        <f t="shared" si="42"/>
+        <v>15</v>
+      </c>
+      <c r="O76" s="10">
+        <v>8</v>
+      </c>
+      <c r="P76" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q76" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="R76" s="26" t="s">
+        <v>278</v>
+      </c>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
+    <row r="77" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>70</v>
+      </c>
+      <c r="B77" s="2">
+        <v>70</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="D77" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="F77" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" s="30">
+        <v>25</v>
+      </c>
+      <c r="H77" s="30">
+        <v>9</v>
+      </c>
+      <c r="I77" s="30">
+        <v>11.5</v>
+      </c>
       <c r="J77" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>54.5</v>
       </c>
       <c r="K77" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>17</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>71.5</v>
       </c>
       <c r="M77" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>71.875</v>
       </c>
       <c r="N77" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="10"/>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-    </row>
-    <row r="78" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
+        <f t="shared" si="42"/>
+        <v>17.25</v>
+      </c>
+      <c r="O77" s="10">
+        <v>8</v>
+      </c>
+      <c r="P77" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q77" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="R77" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="S77" s="26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>80</v>
+      </c>
+      <c r="B78" s="2">
+        <v>75</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" s="4">
+        <v>27</v>
+      </c>
+      <c r="H78" s="4">
+        <v>14</v>
+      </c>
+      <c r="I78" s="4">
+        <v>12</v>
+      </c>
       <c r="J78" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>61</v>
       </c>
       <c r="K78" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>20.5</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>81.5</v>
       </c>
       <c r="M78" s="13">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>75</v>
       </c>
       <c r="N78" s="13">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
-      <c r="R78" s="10"/>
-      <c r="S78" s="10"/>
-    </row>
-    <row r="79" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
+        <f t="shared" si="42"/>
+        <v>18</v>
+      </c>
+      <c r="O78" s="10">
+        <v>8</v>
+      </c>
+      <c r="P78" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q78" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="R78" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="S78" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>60</v>
+      </c>
+      <c r="B79" s="2">
+        <v>65</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" s="30">
+        <v>12</v>
+      </c>
+      <c r="H79" s="30">
+        <v>30</v>
+      </c>
+      <c r="I79" s="30">
+        <v>10.5</v>
+      </c>
       <c r="J79" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K79" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L79" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M79" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>65.625</v>
       </c>
       <c r="N79" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
+        <v>15.75</v>
+      </c>
+      <c r="O79" s="10">
+        <v>9</v>
+      </c>
+      <c r="P79" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q79" s="26" t="s">
+        <v>274</v>
+      </c>
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
+    <row r="80" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="30"/>
+      <c r="D80" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G80" s="30">
+        <v>10</v>
+      </c>
+      <c r="H80" s="30">
+        <v>35</v>
+      </c>
+      <c r="I80" s="30">
+        <v>10.5</v>
+      </c>
       <c r="J80" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="K80" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="L80" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M80" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>65.625</v>
       </c>
       <c r="N80" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O80" s="10"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="10"/>
-      <c r="R80" s="10"/>
+        <v>15.75</v>
+      </c>
+      <c r="O80" s="10">
+        <v>9</v>
+      </c>
+      <c r="P80" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q80" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="R80" s="26" t="s">
+        <v>286</v>
+      </c>
       <c r="S80" s="10"/>
     </row>
-    <row r="81" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
+    <row r="81" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>75</v>
+      </c>
+      <c r="B81" s="2">
+        <v>80</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81" s="4">
+        <v>25</v>
+      </c>
+      <c r="H81" s="4">
+        <v>13</v>
+      </c>
+      <c r="I81" s="4">
+        <v>12.7</v>
+      </c>
       <c r="J81" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>56.5</v>
       </c>
       <c r="K81" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L81" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="M81" s="13">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>79.375</v>
       </c>
       <c r="N81" s="13">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O81" s="10"/>
-      <c r="P81" s="10"/>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-    </row>
-    <row r="82" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="10"/>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="O81" s="10">
+        <v>9</v>
+      </c>
+      <c r="P81" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q81" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="R81" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="S81" s="26" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="26"/>
       <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
+      <c r="E82" s="26"/>
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="10"/>
       <c r="J82" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K82" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L82" s="12">
-        <f t="shared" ref="L82:L102" si="33">J82+K82</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M82" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N82" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O82" s="10"/>
@@ -5191,7 +5874,7 @@
       <c r="R82" s="10"/>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
@@ -5200,23 +5883,23 @@
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K83" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L83" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M83" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N83" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O83" s="10"/>
@@ -5225,7 +5908,7 @@
       <c r="R83" s="10"/>
       <c r="S83" s="10"/>
     </row>
-    <row r="84" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
@@ -5234,23 +5917,23 @@
       <c r="H84" s="10"/>
       <c r="I84" s="10"/>
       <c r="J84" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K84" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L84" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M84" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N84" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O84" s="10"/>
@@ -5259,7 +5942,7 @@
       <c r="R84" s="10"/>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
@@ -5268,23 +5951,23 @@
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
       <c r="J85" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K85" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L85" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M85" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N85" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O85" s="10"/>
@@ -5293,7 +5976,7 @@
       <c r="R85" s="10"/>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
@@ -5302,23 +5985,23 @@
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
       <c r="J86" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L86" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M86" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N86" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O86" s="10"/>
@@ -5327,7 +6010,7 @@
       <c r="R86" s="10"/>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
@@ -5336,23 +6019,23 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
       <c r="J87" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K87" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L87" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M87" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N87" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O87" s="10"/>
@@ -5361,7 +6044,7 @@
       <c r="R87" s="10"/>
       <c r="S87" s="10"/>
     </row>
-    <row r="88" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
@@ -5370,23 +6053,23 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
       <c r="J88" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K88" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M88" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N88" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O88" s="10"/>
@@ -5395,7 +6078,7 @@
       <c r="R88" s="10"/>
       <c r="S88" s="10"/>
     </row>
-    <row r="89" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
@@ -5404,23 +6087,23 @@
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K89" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M89" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N89" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="O89" s="10"/>
@@ -5429,7 +6112,7 @@
       <c r="R89" s="10"/>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
       <c r="E90" s="10"/>
@@ -5446,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="L90" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="L90:L110" si="43">J90+K90</f>
         <v>0</v>
       </c>
       <c r="M90" s="13">
@@ -5463,7 +6146,7 @@
       <c r="R90" s="10"/>
       <c r="S90" s="10"/>
     </row>
-    <row r="91" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
       <c r="E91" s="10"/>
@@ -5480,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M91" s="13">
@@ -5497,7 +6180,7 @@
       <c r="R91" s="10"/>
       <c r="S91" s="10"/>
     </row>
-    <row r="92" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
       <c r="E92" s="10"/>
@@ -5514,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M92" s="13">
@@ -5531,7 +6214,7 @@
       <c r="R92" s="10"/>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
       <c r="E93" s="10"/>
@@ -5548,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M93" s="13">
@@ -5565,7 +6248,7 @@
       <c r="R93" s="10"/>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
@@ -5578,11 +6261,11 @@
         <v>0</v>
       </c>
       <c r="K94" s="10">
-        <f t="shared" ref="K94:K138" si="34">(G94*$I$5)+(H94*$I$6)+(I94*$I$7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L94" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M94" s="13">
@@ -5599,7 +6282,7 @@
       <c r="R94" s="10"/>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
       <c r="E95" s="10"/>
@@ -5612,19 +6295,19 @@
         <v>0</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L95" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M95" s="13">
-        <f t="shared" ref="M95:M138" si="35">I95*$M$2</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N95" s="13">
-        <f t="shared" ref="N95:N138" si="36">I95*$M$3</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O95" s="10"/>
@@ -5633,7 +6316,7 @@
       <c r="R95" s="10"/>
       <c r="S95" s="10"/>
     </row>
-    <row r="96" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
       <c r="E96" s="10"/>
@@ -5646,19 +6329,19 @@
         <v>0</v>
       </c>
       <c r="K96" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L96" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M96" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N96" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O96" s="10"/>
@@ -5680,19 +6363,19 @@
         <v>0</v>
       </c>
       <c r="K97" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L97" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M97" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N97" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O97" s="10"/>
@@ -5714,19 +6397,19 @@
         <v>0</v>
       </c>
       <c r="K98" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L98" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M98" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N98" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O98" s="10"/>
@@ -5748,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="K99" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L99" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M99" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N99" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O99" s="10"/>
@@ -5782,19 +6465,19 @@
         <v>0</v>
       </c>
       <c r="K100" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L100" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M100" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N100" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O100" s="10"/>
@@ -5816,19 +6499,19 @@
         <v>0</v>
       </c>
       <c r="K101" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M101" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N101" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O101" s="10"/>
@@ -5850,19 +6533,19 @@
         <v>0</v>
       </c>
       <c r="K102" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="K102:K146" si="44">(G102*$I$5)+(H102*$I$6)+(I102*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L102" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M102" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N102" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O102" s="10"/>
@@ -5880,23 +6563,23 @@
       <c r="H103" s="10"/>
       <c r="I103" s="10"/>
       <c r="J103" s="23">
-        <f t="shared" ref="J103:J138" si="37">(G103*$I$2)+(H103*$I$3)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K103" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" ref="L103:L138" si="38">J103+K103</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M103" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="M103:M146" si="45">I103*$M$2</f>
         <v>0</v>
       </c>
       <c r="N103" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="N103:N146" si="46">I103*$M$3</f>
         <v>0</v>
       </c>
       <c r="O103" s="10"/>
@@ -5914,23 +6597,23 @@
       <c r="H104" s="10"/>
       <c r="I104" s="10"/>
       <c r="J104" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K104" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M104" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N104" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O104" s="10"/>
@@ -5948,23 +6631,23 @@
       <c r="H105" s="10"/>
       <c r="I105" s="10"/>
       <c r="J105" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K105" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L105" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M105" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N105" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O105" s="10"/>
@@ -5982,23 +6665,23 @@
       <c r="H106" s="10"/>
       <c r="I106" s="10"/>
       <c r="J106" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K106" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L106" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M106" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N106" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O106" s="10"/>
@@ -6016,23 +6699,23 @@
       <c r="H107" s="10"/>
       <c r="I107" s="10"/>
       <c r="J107" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K107" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L107" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M107" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N107" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O107" s="10"/>
@@ -6050,23 +6733,23 @@
       <c r="H108" s="10"/>
       <c r="I108" s="10"/>
       <c r="J108" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K108" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L108" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M108" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N108" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O108" s="10"/>
@@ -6084,23 +6767,23 @@
       <c r="H109" s="10"/>
       <c r="I109" s="10"/>
       <c r="J109" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K109" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L109" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N109" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O109" s="10"/>
@@ -6118,23 +6801,23 @@
       <c r="H110" s="10"/>
       <c r="I110" s="10"/>
       <c r="J110" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K110" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L110" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M110" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N110" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O110" s="10"/>
@@ -6152,23 +6835,23 @@
       <c r="H111" s="10"/>
       <c r="I111" s="10"/>
       <c r="J111" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="J111:J146" si="47">(G111*$I$2)+(H111*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K111" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L111" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="L111:L146" si="48">J111+K111</f>
         <v>0</v>
       </c>
       <c r="M111" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N111" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O111" s="10"/>
@@ -6186,23 +6869,23 @@
       <c r="H112" s="10"/>
       <c r="I112" s="10"/>
       <c r="J112" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K112" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L112" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M112" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N112" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O112" s="10"/>
@@ -6220,23 +6903,23 @@
       <c r="H113" s="10"/>
       <c r="I113" s="10"/>
       <c r="J113" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K113" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L113" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M113" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N113" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O113" s="10"/>
@@ -6254,23 +6937,23 @@
       <c r="H114" s="10"/>
       <c r="I114" s="10"/>
       <c r="J114" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K114" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L114" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M114" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N114" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O114" s="10"/>
@@ -6288,23 +6971,23 @@
       <c r="H115" s="10"/>
       <c r="I115" s="10"/>
       <c r="J115" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K115" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L115" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M115" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N115" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O115" s="10"/>
@@ -6322,23 +7005,23 @@
       <c r="H116" s="10"/>
       <c r="I116" s="10"/>
       <c r="J116" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K116" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L116" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M116" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N116" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O116" s="10"/>
@@ -6356,23 +7039,23 @@
       <c r="H117" s="10"/>
       <c r="I117" s="10"/>
       <c r="J117" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K117" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L117" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M117" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N117" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O117" s="10"/>
@@ -6390,23 +7073,23 @@
       <c r="H118" s="10"/>
       <c r="I118" s="10"/>
       <c r="J118" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K118" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L118" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M118" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N118" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O118" s="10"/>
@@ -6424,23 +7107,23 @@
       <c r="H119" s="10"/>
       <c r="I119" s="10"/>
       <c r="J119" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K119" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L119" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M119" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N119" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O119" s="10"/>
@@ -6458,23 +7141,23 @@
       <c r="H120" s="10"/>
       <c r="I120" s="10"/>
       <c r="J120" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K120" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L120" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M120" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N120" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O120" s="10"/>
@@ -6492,23 +7175,23 @@
       <c r="H121" s="10"/>
       <c r="I121" s="10"/>
       <c r="J121" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K121" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L121" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M121" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N121" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O121" s="10"/>
@@ -6526,23 +7209,23 @@
       <c r="H122" s="10"/>
       <c r="I122" s="10"/>
       <c r="J122" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K122" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L122" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M122" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N122" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O122" s="10"/>
@@ -6560,23 +7243,23 @@
       <c r="H123" s="10"/>
       <c r="I123" s="10"/>
       <c r="J123" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K123" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L123" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M123" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N123" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O123" s="10"/>
@@ -6594,23 +7277,23 @@
       <c r="H124" s="10"/>
       <c r="I124" s="10"/>
       <c r="J124" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K124" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L124" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M124" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N124" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O124" s="10"/>
@@ -6628,23 +7311,23 @@
       <c r="H125" s="10"/>
       <c r="I125" s="10"/>
       <c r="J125" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K125" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L125" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M125" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N125" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O125" s="10"/>
@@ -6662,23 +7345,23 @@
       <c r="H126" s="10"/>
       <c r="I126" s="10"/>
       <c r="J126" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K126" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L126" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M126" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N126" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O126" s="10"/>
@@ -6696,23 +7379,23 @@
       <c r="H127" s="10"/>
       <c r="I127" s="10"/>
       <c r="J127" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K127" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L127" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M127" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N127" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O127" s="10"/>
@@ -6730,23 +7413,23 @@
       <c r="H128" s="10"/>
       <c r="I128" s="10"/>
       <c r="J128" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K128" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L128" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M128" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N128" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O128" s="10"/>
@@ -6764,23 +7447,23 @@
       <c r="H129" s="10"/>
       <c r="I129" s="10"/>
       <c r="J129" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K129" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L129" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M129" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N129" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O129" s="10"/>
@@ -6798,23 +7481,23 @@
       <c r="H130" s="10"/>
       <c r="I130" s="10"/>
       <c r="J130" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K130" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L130" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M130" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N130" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O130" s="10"/>
@@ -6832,23 +7515,23 @@
       <c r="H131" s="10"/>
       <c r="I131" s="10"/>
       <c r="J131" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K131" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L131" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M131" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N131" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O131" s="10"/>
@@ -6866,23 +7549,23 @@
       <c r="H132" s="10"/>
       <c r="I132" s="10"/>
       <c r="J132" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K132" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L132" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M132" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N132" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O132" s="10"/>
@@ -6900,23 +7583,23 @@
       <c r="H133" s="10"/>
       <c r="I133" s="10"/>
       <c r="J133" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K133" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L133" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M133" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N133" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O133" s="10"/>
@@ -6934,23 +7617,23 @@
       <c r="H134" s="10"/>
       <c r="I134" s="10"/>
       <c r="J134" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K134" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L134" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M134" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N134" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O134" s="10"/>
@@ -6968,23 +7651,23 @@
       <c r="H135" s="10"/>
       <c r="I135" s="10"/>
       <c r="J135" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K135" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L135" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M135" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N135" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O135" s="10"/>
@@ -7002,23 +7685,23 @@
       <c r="H136" s="10"/>
       <c r="I136" s="10"/>
       <c r="J136" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K136" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L136" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M136" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N136" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O136" s="10"/>
@@ -7036,23 +7719,23 @@
       <c r="H137" s="10"/>
       <c r="I137" s="10"/>
       <c r="J137" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K137" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L137" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M137" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N137" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O137" s="10"/>
@@ -7070,23 +7753,23 @@
       <c r="H138" s="10"/>
       <c r="I138" s="10"/>
       <c r="J138" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K138" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L138" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M138" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N138" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="O138" s="10"/>
@@ -7094,6 +7777,278 @@
       <c r="Q138" s="10"/>
       <c r="R138" s="10"/>
       <c r="S138" s="10"/>
+    </row>
+    <row r="139" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C139" s="10"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
+      <c r="G139" s="10"/>
+      <c r="H139" s="10"/>
+      <c r="I139" s="10"/>
+      <c r="J139" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K139" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L139" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M139" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N139" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O139" s="10"/>
+      <c r="P139" s="10"/>
+      <c r="Q139" s="10"/>
+      <c r="R139" s="10"/>
+      <c r="S139" s="10"/>
+    </row>
+    <row r="140" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="10"/>
+      <c r="H140" s="10"/>
+      <c r="I140" s="10"/>
+      <c r="J140" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K140" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M140" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N140" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O140" s="10"/>
+      <c r="P140" s="10"/>
+      <c r="Q140" s="10"/>
+      <c r="R140" s="10"/>
+      <c r="S140" s="10"/>
+    </row>
+    <row r="141" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C141" s="10"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="10"/>
+      <c r="H141" s="10"/>
+      <c r="I141" s="10"/>
+      <c r="J141" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K141" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L141" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M141" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N141" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O141" s="10"/>
+      <c r="P141" s="10"/>
+      <c r="Q141" s="10"/>
+      <c r="R141" s="10"/>
+      <c r="S141" s="10"/>
+    </row>
+    <row r="142" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+      <c r="H142" s="10"/>
+      <c r="I142" s="10"/>
+      <c r="J142" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K142" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L142" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M142" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N142" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O142" s="10"/>
+      <c r="P142" s="10"/>
+      <c r="Q142" s="10"/>
+      <c r="R142" s="10"/>
+      <c r="S142" s="10"/>
+    </row>
+    <row r="143" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="10"/>
+      <c r="H143" s="10"/>
+      <c r="I143" s="10"/>
+      <c r="J143" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K143" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N143" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O143" s="10"/>
+      <c r="P143" s="10"/>
+      <c r="Q143" s="10"/>
+      <c r="R143" s="10"/>
+      <c r="S143" s="10"/>
+    </row>
+    <row r="144" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="10"/>
+      <c r="H144" s="10"/>
+      <c r="I144" s="10"/>
+      <c r="J144" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K144" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L144" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N144" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O144" s="10"/>
+      <c r="P144" s="10"/>
+      <c r="Q144" s="10"/>
+      <c r="R144" s="10"/>
+      <c r="S144" s="10"/>
+    </row>
+    <row r="145" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10"/>
+      <c r="H145" s="10"/>
+      <c r="I145" s="10"/>
+      <c r="J145" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K145" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L145" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M145" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N145" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O145" s="10"/>
+      <c r="P145" s="10"/>
+      <c r="Q145" s="10"/>
+      <c r="R145" s="10"/>
+      <c r="S145" s="10"/>
+    </row>
+    <row r="146" spans="3:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="10"/>
+      <c r="H146" s="10"/>
+      <c r="I146" s="10"/>
+      <c r="J146" s="23">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K146" s="10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L146" s="12">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M146" s="13">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N146" s="13">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O146" s="10"/>
+      <c r="P146" s="10"/>
+      <c r="Q146" s="10"/>
+      <c r="R146" s="10"/>
+      <c r="S146" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7146,10 +8101,10 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C2" s="4">
         <v>5.5</v>
@@ -7167,7 +8122,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="12"/>
@@ -7176,10 +8131,10 @@
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C3" s="4">
         <v>3</v>
@@ -7197,10 +8152,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
@@ -7208,10 +8163,10 @@
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C4" s="4">
         <v>7.5</v>
@@ -7229,7 +8184,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="12"/>
@@ -7238,10 +8193,10 @@
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C5" s="9">
         <v>7</v>
@@ -7259,7 +8214,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="12"/>

--- a/dev_docs/Tetra数值公式_11_4.xlsx
+++ b/dev_docs/Tetra数值公式_11_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCL\.minecraft\versions\SenDims_BanForges\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9DC169-E8C4-4BC9-96AF-3956235E5830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E67EF8-B0B2-4DF2-B30B-B0F6E89AF303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="294">
   <si>
     <t>刀刃</t>
   </si>
@@ -771,9 +771,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>'ad_astra:infernal_spire_block'</t>
-  </si>
-  <si>
     <t>耐热金属</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -983,6 +980,21 @@
   </si>
   <si>
     <t>冰霜伤害+6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ad_astra:infernal_spire_block'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫菘玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>'integratedterminals:chorus_glass'</t>
+  </si>
+  <si>
+    <t>行动力效率+10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4758,8 +4770,8 @@
       <c r="C63" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>236</v>
+      <c r="D63" s="32" t="s">
+        <v>290</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>235</v>
@@ -4803,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="Q63" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
@@ -4855,7 +4867,7 @@
         <v>4</v>
       </c>
       <c r="Q64" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R64" s="10"/>
       <c r="S64" s="10"/>
@@ -4907,7 +4919,7 @@
         <v>4</v>
       </c>
       <c r="Q65" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R65" s="10"/>
       <c r="S65" s="10"/>
@@ -4923,10 +4935,10 @@
         <v>211</v>
       </c>
       <c r="D66" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F66" s="30" t="s">
         <v>57</v>
@@ -4967,7 +4979,7 @@
         <v>5</v>
       </c>
       <c r="Q66" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R66" s="10"/>
       <c r="S66" s="10"/>
@@ -4975,10 +4987,10 @@
     <row r="67" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="30"/>
       <c r="D67" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>57</v>
@@ -5025,7 +5037,7 @@
         <v>174</v>
       </c>
       <c r="S67" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -5092,31 +5104,43 @@
     </row>
     <row r="69" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
+      <c r="D69" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" s="4">
+        <v>17</v>
+      </c>
+      <c r="H69" s="4">
+        <v>2</v>
+      </c>
+      <c r="I69" s="4">
+        <v>7</v>
+      </c>
       <c r="J69" s="23">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K69" s="10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="L69" s="12">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="M69" s="13">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="N69" s="13">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O69" s="10">
         <v>6</v>
@@ -5124,8 +5148,12 @@
       <c r="P69" s="10">
         <v>6</v>
       </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
+      <c r="Q69" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="R69" s="26" t="s">
+        <v>269</v>
+      </c>
       <c r="S69" s="10"/>
     </row>
     <row r="70" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -5136,13 +5164,13 @@
         <v>50</v>
       </c>
       <c r="C70" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" s="30" t="s">
         <v>238</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="E70" s="30" t="s">
-        <v>239</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>57</v>
@@ -5183,7 +5211,7 @@
         <v>6</v>
       </c>
       <c r="Q70" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R70" s="26" t="s">
         <v>227</v>
@@ -5201,10 +5229,10 @@
         <v>202</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>57</v>
@@ -5245,7 +5273,7 @@
         <v>7</v>
       </c>
       <c r="Q71" s="26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R71" s="10"/>
       <c r="S71" s="10"/>
@@ -5258,13 +5286,13 @@
         <v>60</v>
       </c>
       <c r="C72" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="E72" s="30" t="s">
         <v>242</v>
-      </c>
-      <c r="D72" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="E72" s="30" t="s">
-        <v>243</v>
       </c>
       <c r="F72" s="30" t="s">
         <v>57</v>
@@ -5305,7 +5333,7 @@
         <v>7</v>
       </c>
       <c r="Q72" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R72" s="10"/>
       <c r="S72" s="10"/>
@@ -5313,10 +5341,10 @@
     <row r="73" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="30"/>
       <c r="D73" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>57</v>
@@ -5357,7 +5385,7 @@
         <v>7</v>
       </c>
       <c r="Q73" s="26" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R73" s="26" t="s">
         <v>231</v>
@@ -5372,13 +5400,13 @@
         <v>65</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>57</v>
@@ -5419,20 +5447,20 @@
         <v>8</v>
       </c>
       <c r="Q74" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="R74" s="26" t="s">
         <v>276</v>
-      </c>
-      <c r="R74" s="26" t="s">
-        <v>277</v>
       </c>
       <c r="S74" s="10"/>
     </row>
     <row r="75" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="4"/>
       <c r="D75" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>57</v>
@@ -5473,20 +5501,20 @@
         <v>8</v>
       </c>
       <c r="Q75" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R75" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S75" s="10"/>
     </row>
     <row r="76" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="4"/>
       <c r="D76" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>57</v>
@@ -5527,10 +5555,10 @@
         <v>8</v>
       </c>
       <c r="Q76" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R76" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S76" s="10"/>
     </row>
@@ -5542,13 +5570,13 @@
         <v>70</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D77" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E77" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F77" s="30" t="s">
         <v>57</v>
@@ -5589,13 +5617,13 @@
         <v>9</v>
       </c>
       <c r="Q77" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="R77" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="R77" s="26" t="s">
+      <c r="S77" s="26" t="s">
         <v>282</v>
-      </c>
-      <c r="S77" s="26" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -5606,13 +5634,13 @@
         <v>75</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>57</v>
@@ -5653,13 +5681,13 @@
         <v>9</v>
       </c>
       <c r="Q78" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R78" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S78" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -5673,7 +5701,7 @@
         <v>203</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E79" s="30" t="s">
         <v>204</v>
@@ -5717,7 +5745,7 @@
         <v>9</v>
       </c>
       <c r="Q79" s="26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
@@ -5725,42 +5753,42 @@
     <row r="80" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="30"/>
       <c r="D80" s="33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E80" s="30" t="s">
         <v>212</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>221</v>
+        <v>57</v>
       </c>
       <c r="G80" s="30">
         <v>10</v>
       </c>
       <c r="H80" s="30">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I80" s="30">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="J80" s="23">
         <f t="shared" si="28"/>
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="K80" s="10">
         <f t="shared" si="29"/>
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="L80" s="12">
         <f t="shared" si="30"/>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M80" s="13">
         <f t="shared" si="31"/>
-        <v>65.625</v>
+        <v>43.75</v>
       </c>
       <c r="N80" s="13">
         <f t="shared" si="32"/>
-        <v>15.75</v>
+        <v>10.5</v>
       </c>
       <c r="O80" s="10">
         <v>9</v>
@@ -5769,10 +5797,10 @@
         <v>10</v>
       </c>
       <c r="Q80" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="R80" s="26" t="s">
         <v>285</v>
-      </c>
-      <c r="R80" s="26" t="s">
-        <v>286</v>
       </c>
       <c r="S80" s="10"/>
     </row>
@@ -5787,7 +5815,7 @@
         <v>206</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>205</v>
@@ -5831,13 +5859,13 @@
         <v>10</v>
       </c>
       <c r="Q81" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="R81" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="R81" s="26" t="s">
+      <c r="S81" s="26" t="s">
         <v>288</v>
-      </c>
-      <c r="S81" s="26" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="82" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -8053,12 +8081,13 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -8067,7 +8096,7 @@
     <col min="9" max="9" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
@@ -8099,255 +8128,645 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>228</v>
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="C2" s="4">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="F2" s="10">
+        <v>4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>4</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+    </row>
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="D3" s="4">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="F3" s="10">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10">
+        <v>4</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+    </row>
+    <row r="4" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="4">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="10">
+        <v>5</v>
+      </c>
+      <c r="G4" s="10">
+        <v>4</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="30">
+        <v>9</v>
+      </c>
+      <c r="D5" s="30">
+        <v>12</v>
+      </c>
+      <c r="E5" s="30">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="30">
+        <v>12</v>
+      </c>
+      <c r="D6" s="30">
+        <v>5</v>
+      </c>
+      <c r="E6" s="30">
+        <v>6.5</v>
+      </c>
+      <c r="F6" s="10">
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>5</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="4">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4">
+        <v>7</v>
+      </c>
+      <c r="F7" s="10">
+        <v>6</v>
+      </c>
+      <c r="G7" s="10">
+        <v>5</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="4">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="G2" s="10">
-        <v>2</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="E8" s="4">
+        <v>7</v>
+      </c>
+      <c r="F8" s="10">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
-        <v>3</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="G8" s="10">
+        <v>6</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="30">
+        <v>15.5</v>
+      </c>
+      <c r="D9" s="30">
+        <v>6</v>
+      </c>
+      <c r="E9" s="30">
+        <v>8</v>
+      </c>
+      <c r="F9" s="10">
+        <v>6</v>
+      </c>
+      <c r="G9" s="10">
+        <v>6</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="4">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4">
         <v>7.5</v>
       </c>
-      <c r="D4" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="F4" s="10">
-        <v>2</v>
-      </c>
-      <c r="G4" s="10">
-        <v>2</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="F10" s="10">
+        <v>6</v>
+      </c>
+      <c r="G10" s="10">
         <v>7</v>
       </c>
-      <c r="D5" s="9">
-        <v>6</v>
-      </c>
-      <c r="E5" s="9">
-        <v>3.2</v>
-      </c>
-      <c r="F5" s="10">
-        <v>3</v>
-      </c>
-      <c r="G5" s="10">
-        <v>3</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11"/>
+      <c r="H10" s="26" t="s">
+        <v>273</v>
+      </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="30">
+        <v>17</v>
+      </c>
+      <c r="D11" s="30">
+        <v>7</v>
+      </c>
+      <c r="E11" s="30">
+        <v>9.5</v>
+      </c>
+      <c r="F11" s="10">
+        <v>7</v>
+      </c>
+      <c r="G11" s="10">
+        <v>7</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>289</v>
+      </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="30">
+        <v>18</v>
+      </c>
+      <c r="D12" s="30">
+        <v>10</v>
+      </c>
+      <c r="E12" s="30">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F12" s="10">
+        <v>7</v>
+      </c>
+      <c r="G12" s="10">
+        <v>7</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>231</v>
+      </c>
       <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="4">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4">
+        <v>10</v>
+      </c>
+      <c r="F13" s="10">
+        <v>8</v>
+      </c>
+      <c r="G13" s="10">
+        <v>8</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>276</v>
+      </c>
       <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="4">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4">
+        <v>11</v>
+      </c>
+      <c r="F14" s="10">
+        <v>8</v>
+      </c>
+      <c r="G14" s="10">
+        <v>8</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>279</v>
+      </c>
       <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:14" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="4">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4">
+        <v>10</v>
+      </c>
+      <c r="F15" s="10">
+        <v>8</v>
+      </c>
+      <c r="G15" s="10">
+        <v>8</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>277</v>
+      </c>
       <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="30">
+        <v>25</v>
+      </c>
+      <c r="D16" s="30">
+        <v>9</v>
+      </c>
+      <c r="E16" s="30">
+        <v>11.5</v>
+      </c>
+      <c r="F16" s="10">
+        <v>8</v>
+      </c>
+      <c r="G16" s="10">
+        <v>9</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="4">
+        <v>27</v>
+      </c>
+      <c r="D17" s="4">
+        <v>14</v>
+      </c>
+      <c r="E17" s="4">
+        <v>12</v>
+      </c>
+      <c r="F17" s="10">
+        <v>8</v>
+      </c>
+      <c r="G17" s="10">
+        <v>9</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="I17" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="K17" s="10"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="30">
+        <v>12</v>
+      </c>
+      <c r="D18" s="30">
+        <v>30</v>
+      </c>
+      <c r="E18" s="30">
+        <v>10.5</v>
+      </c>
+      <c r="F18" s="10">
+        <v>9</v>
+      </c>
+      <c r="G18" s="10">
+        <v>9</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="30">
+        <v>10</v>
+      </c>
+      <c r="D19" s="30">
+        <v>15</v>
+      </c>
+      <c r="E19" s="30">
+        <v>7</v>
+      </c>
+      <c r="F19" s="10">
+        <v>9</v>
+      </c>
+      <c r="G19" s="10">
+        <v>10</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" s="4">
+        <v>25</v>
+      </c>
+      <c r="D20" s="4">
+        <v>13</v>
+      </c>
+      <c r="E20" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="F20" s="10">
+        <v>9</v>
+      </c>
+      <c r="G20" s="10">
+        <v>10</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
